--- a/Factory_to_Customer_Shipping_Route_Efficiency_Analysis/Dataset/Roadmap.xlsx
+++ b/Factory_to_Customer_Shipping_Route_Efficiency_Analysis/Dataset/Roadmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\THE CODE\PROJECTS\Factory_to_Customer_Shipping_Route_Efficiency_Analysis\Dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C5E3C22-B2E4-4245-BF64-252E6563F142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8FE000-2114-4469-B3B7-7D9313B39395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -112,7 +112,9 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-sales / units</t>
+price per unit -- sales / units
+profit per unit -- gross profit / units
+cost per unit -- cost / units</t>
         </r>
       </text>
     </comment>
@@ -121,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
   <si>
     <t>Row ID</t>
   </si>
@@ -177,9 +179,6 @@
     <t>Cost</t>
   </si>
   <si>
-    <t>Price per unit</t>
-  </si>
-  <si>
     <t>REMOVE</t>
   </si>
   <si>
@@ -229,6 +228,23 @@
   </si>
   <si>
     <t>Product Category</t>
+  </si>
+  <si>
+    <t>Price per unit
+Profit per unit
+Cost per unit</t>
+  </si>
+  <si>
+    <t>Gross Profit Per Order</t>
+  </si>
+  <si>
+    <t>Sales Per Order</t>
+  </si>
+  <si>
+    <t>Units Per Order</t>
+  </si>
+  <si>
+    <t>Total Cost Per Order</t>
   </si>
 </sst>
 </file>
@@ -318,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -340,6 +356,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -634,16 +653,16 @@
     <row r="3" spans="3:7" ht="18" x14ac:dyDescent="0.35">
       <c r="C3" s="1"/>
       <c r="D3" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="3:7" x14ac:dyDescent="0.3">
@@ -654,7 +673,7 @@
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="3:7" x14ac:dyDescent="0.3">
@@ -665,7 +684,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="3:7" x14ac:dyDescent="0.3">
@@ -673,10 +692,10 @@
         <v>2</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -686,11 +705,11 @@
         <v>3</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G7" s="1"/>
     </row>
@@ -699,11 +718,11 @@
         <v>4</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G8" s="1"/>
     </row>
@@ -715,7 +734,7 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="3:7" x14ac:dyDescent="0.3">
@@ -723,11 +742,11 @@
         <v>6</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G10" s="1"/>
     </row>
@@ -736,7 +755,7 @@
         <v>7</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -747,11 +766,11 @@
         <v>8</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G12" s="1"/>
     </row>
@@ -769,11 +788,11 @@
         <v>10</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G14" s="1"/>
     </row>
@@ -782,7 +801,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -796,7 +815,7 @@
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="3:7" x14ac:dyDescent="0.3">
@@ -804,7 +823,7 @@
         <v>13</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -815,12 +834,14 @@
         <v>14</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="3:7" x14ac:dyDescent="0.3">
@@ -828,10 +849,12 @@
         <v>15</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
+      <c r="F19" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="3:7" x14ac:dyDescent="0.3">
@@ -839,25 +862,29 @@
         <v>16</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="G21" s="1"/>
     </row>
   </sheetData>
